--- a/public/example/Template_Question_Bank_Import.xlsx
+++ b/public/example/Template_Question_Bank_Import.xlsx
@@ -1,22 +1,29 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="24334"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\school_system\public\example\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{81F8BF11-C8A6-4A17-A45A-D37255D831C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12525"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Pilihan Ganda" sheetId="1" r:id="rId1"/>
     <sheet name="Pilihan Ganda Kompleks" sheetId="2" r:id="rId2"/>
     <sheet name="Benar Salah" sheetId="3" r:id="rId3"/>
+    <sheet name="Soal Uraian" sheetId="4" r:id="rId4"/>
   </sheets>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="47">
   <si>
     <t>No</t>
   </si>
@@ -148,19 +155,22 @@
   </si>
   <si>
     <t>Salah</t>
+  </si>
+  <si>
+    <t>Buatlah sebuah pantun nasihat sesuai kaidah penulisan pantun!</t>
+  </si>
+  <si>
+    <t>Jelaskan perbedaan antara ringkasan dan ikhtisar!</t>
+  </si>
+  <si>
+    <t>Buatlah contoh teks prosedur cara membuat jus buah!</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="4">
-    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;_);_(@_)"/>
-    <numFmt numFmtId="44" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
-  </numFmts>
-  <fonts count="28">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="10">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -213,157 +223,17 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="Aptos Narrow"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
+      <color rgb="FF333333"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
-      <color theme="0"/>
-      <name val="Aptos Narrow"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="Aptos Narrow"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="Aptos Narrow"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Aptos Narrow"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="Aptos Narrow"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="Aptos Narrow"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="Aptos Narrow"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="Aptos Narrow"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="Aptos Narrow"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Aptos Narrow"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="Aptos Narrow"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="Aptos Narrow"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="Aptos Narrow"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="Aptos Narrow"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="Aptos Narrow"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="Aptos Narrow"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="Aptos Narrow"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="Aptos Narrow"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="Aptos Narrow"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
   </fonts>
-  <fills count="35">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -372,204 +242,18 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
+        <fgColor theme="7" tint="0.59999389629810485"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
+        <fgColor theme="6" tint="0.59999389629810485"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="13">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -634,252 +318,23 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
-        <color rgb="FFB2B2B2"/>
+        <color rgb="FF000000"/>
       </left>
       <right style="thin">
-        <color rgb="FFB2B2B2"/>
+        <color rgb="FF000000"/>
       </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
+      <top/>
       <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
+        <color rgb="FF000000"/>
       </bottom>
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="49">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="10" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="8" borderId="7" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="29" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="10" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="7" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -926,69 +381,37 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="49">
+  <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="60% - Accent6" xfId="1" builtinId="52"/>
-    <cellStyle name="40% - Accent6" xfId="2" builtinId="51"/>
-    <cellStyle name="60% - Accent5" xfId="3" builtinId="48"/>
-    <cellStyle name="Accent6" xfId="4" builtinId="49"/>
-    <cellStyle name="40% - Accent5" xfId="5" builtinId="47"/>
-    <cellStyle name="20% - Accent5" xfId="6" builtinId="46"/>
-    <cellStyle name="60% - Accent4" xfId="7" builtinId="44"/>
-    <cellStyle name="Accent5" xfId="8" builtinId="45"/>
-    <cellStyle name="40% - Accent4" xfId="9" builtinId="43"/>
-    <cellStyle name="Accent4" xfId="10" builtinId="41"/>
-    <cellStyle name="Linked Cell" xfId="11" builtinId="24"/>
-    <cellStyle name="40% - Accent3" xfId="12" builtinId="39"/>
-    <cellStyle name="60% - Accent2" xfId="13" builtinId="36"/>
-    <cellStyle name="Accent3" xfId="14" builtinId="37"/>
-    <cellStyle name="40% - Accent2" xfId="15" builtinId="35"/>
-    <cellStyle name="20% - Accent2" xfId="16" builtinId="34"/>
-    <cellStyle name="Accent2" xfId="17" builtinId="33"/>
-    <cellStyle name="40% - Accent1" xfId="18" builtinId="31"/>
-    <cellStyle name="20% - Accent1" xfId="19" builtinId="30"/>
-    <cellStyle name="Accent1" xfId="20" builtinId="29"/>
-    <cellStyle name="Neutral" xfId="21" builtinId="28"/>
-    <cellStyle name="60% - Accent1" xfId="22" builtinId="32"/>
-    <cellStyle name="Bad" xfId="23" builtinId="27"/>
-    <cellStyle name="20% - Accent4" xfId="24" builtinId="42"/>
-    <cellStyle name="Total" xfId="25" builtinId="25"/>
-    <cellStyle name="Output" xfId="26" builtinId="21"/>
-    <cellStyle name="Currency" xfId="27" builtinId="4"/>
-    <cellStyle name="20% - Accent3" xfId="28" builtinId="38"/>
-    <cellStyle name="Note" xfId="29" builtinId="10"/>
-    <cellStyle name="Input" xfId="30" builtinId="20"/>
-    <cellStyle name="Heading 4" xfId="31" builtinId="19"/>
-    <cellStyle name="Calculation" xfId="32" builtinId="22"/>
-    <cellStyle name="Good" xfId="33" builtinId="26"/>
-    <cellStyle name="Heading 3" xfId="34" builtinId="18"/>
-    <cellStyle name="CExplanatory Text" xfId="35" builtinId="53"/>
-    <cellStyle name="Heading 1" xfId="36" builtinId="16"/>
-    <cellStyle name="Comma [0]" xfId="37" builtinId="6"/>
-    <cellStyle name="20% - Accent6" xfId="38" builtinId="50"/>
-    <cellStyle name="Title" xfId="39" builtinId="15"/>
-    <cellStyle name="Currency [0]" xfId="40" builtinId="7"/>
-    <cellStyle name="Warning Text" xfId="41" builtinId="11"/>
-    <cellStyle name="Followed Hyperlink" xfId="42" builtinId="9"/>
-    <cellStyle name="Heading 2" xfId="43" builtinId="17"/>
-    <cellStyle name="Comma" xfId="44" builtinId="3"/>
-    <cellStyle name="Check Cell" xfId="45" builtinId="23"/>
-    <cellStyle name="60% - Accent3" xfId="46" builtinId="40"/>
-    <cellStyle name="Percent" xfId="47" builtinId="5"/>
-    <cellStyle name="Hyperlink" xfId="48" builtinId="8"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleMedium9"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>2</xdr:col>
@@ -1004,13 +427,19 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="4" name="Gambar 3"/>
+        <xdr:cNvPr id="4" name="Gambar 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000004000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip r:embed="rId1"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1042,13 +471,19 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="5" name="Gambar 4"/>
+        <xdr:cNvPr id="5" name="Gambar 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000005000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip r:embed="rId2"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1080,13 +515,19 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="6" name="Gambar 5"/>
+        <xdr:cNvPr id="6" name="Gambar 5">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000006000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip r:embed="rId3"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1118,13 +559,19 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="8" name="Gambar 7"/>
+        <xdr:cNvPr id="8" name="Gambar 7">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000008000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip r:embed="rId4"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1156,13 +603,19 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="9" name="Gambar 8"/>
+        <xdr:cNvPr id="9" name="Gambar 8">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000009000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip r:embed="rId5"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1194,13 +647,19 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="10" name="Gambar 9"/>
+        <xdr:cNvPr id="10" name="Gambar 9">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00000A000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip r:embed="rId6"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1492,24 +951,24 @@
       </a:style>
     </a:lnDef>
   </a:objectDefaults>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:I5"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" outlineLevelRow="4"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="2" width="4.85333333333333" style="9" customWidth="1"/>
-    <col min="3" max="3" width="43.8533333333333" style="9" customWidth="1"/>
-    <col min="4" max="4" width="13.3333333333333" style="9" customWidth="1"/>
-    <col min="5" max="7" width="34.8533333333333" style="9" customWidth="1"/>
-    <col min="8" max="8" width="34.6666666666667" style="10" customWidth="1"/>
-    <col min="9" max="9" width="34.6666666666667" style="11" customWidth="1"/>
+    <col min="1" max="2" width="4.875" style="9" customWidth="1"/>
+    <col min="3" max="3" width="43.875" style="9" customWidth="1"/>
+    <col min="4" max="4" width="13.375" style="9" customWidth="1"/>
+    <col min="5" max="7" width="34.875" style="9" customWidth="1"/>
+    <col min="8" max="8" width="34.625" style="10" customWidth="1"/>
+    <col min="9" max="9" width="34.625" style="11" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9">
+    <row r="1" spans="1:9" ht="15">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
@@ -1538,7 +997,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" ht="68.25" customHeight="1" spans="1:8">
+    <row r="2" spans="1:9" ht="68.25" customHeight="1">
       <c r="A2" s="2">
         <v>1</v>
       </c>
@@ -1564,7 +1023,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="3" ht="30" spans="1:8">
+    <row r="3" spans="1:9" ht="57">
       <c r="A3" s="2">
         <v>2</v>
       </c>
@@ -1588,7 +1047,7 @@
       </c>
       <c r="H3" s="18"/>
     </row>
-    <row r="4" ht="47" customHeight="1" spans="1:8">
+    <row r="4" spans="1:9" ht="47.1" customHeight="1">
       <c r="A4" s="2">
         <v>3</v>
       </c>
@@ -1606,7 +1065,7 @@
       <c r="G4" s="1"/>
       <c r="H4" s="18"/>
     </row>
-    <row r="5" ht="146.25" customHeight="1" spans="1:8">
+    <row r="5" spans="1:9" ht="146.25" customHeight="1">
       <c r="A5" s="9">
         <v>4</v>
       </c>
@@ -1634,26 +1093,24 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <headerFooter/>
   <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:I3"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" outlineLevelRow="2"/>
+  <sheetFormatPr defaultColWidth="9.125" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="2" width="4.85333333333333" style="1" customWidth="1"/>
-    <col min="3" max="3" width="47.4266666666667" style="1" customWidth="1"/>
-    <col min="4" max="4" width="16.8533333333333" style="1" customWidth="1"/>
-    <col min="5" max="7" width="27.5688888888889" style="1" customWidth="1"/>
+    <col min="1" max="2" width="4.875" style="1" customWidth="1"/>
+    <col min="3" max="3" width="47.375" style="1" customWidth="1"/>
+    <col min="4" max="4" width="16.875" style="1" customWidth="1"/>
+    <col min="5" max="7" width="27.625" style="1" customWidth="1"/>
     <col min="8" max="9" width="28" style="1" customWidth="1"/>
-    <col min="10" max="16384" width="9.14222222222222" style="3"/>
+    <col min="10" max="16384" width="9.125" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9">
+    <row r="1" spans="1:9" ht="15">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
@@ -1682,7 +1139,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" ht="30" spans="1:9">
+    <row r="2" spans="1:9" ht="42.75">
       <c r="A2" s="2">
         <v>1</v>
       </c>
@@ -1711,7 +1168,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="3" ht="39" spans="1:9">
+    <row r="3" spans="1:9" ht="57">
       <c r="A3" s="2">
         <v>2</v>
       </c>
@@ -1742,23 +1199,21 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:D4"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" outlineLevelRow="3" outlineLevelCol="3"/>
+  <sheetFormatPr defaultColWidth="9.125" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="2" width="6.42666666666667" style="1" customWidth="1"/>
-    <col min="3" max="3" width="57.7111111111111" style="1" customWidth="1"/>
-    <col min="4" max="4" width="19.2844444444444" style="2" customWidth="1"/>
-    <col min="5" max="16384" width="9.14222222222222" style="3"/>
+    <col min="1" max="2" width="6.375" style="1" customWidth="1"/>
+    <col min="3" max="3" width="57.75" style="1" customWidth="1"/>
+    <col min="4" max="4" width="19.25" style="2" customWidth="1"/>
+    <col min="5" max="16384" width="9.125" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4">
+    <row r="1" spans="1:4" ht="15">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
@@ -1772,7 +1227,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="2" spans="1:4">
+    <row r="2" spans="1:4" ht="28.5">
       <c r="A2" s="2">
         <v>1</v>
       </c>
@@ -1786,7 +1241,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="3" spans="1:4">
+    <row r="3" spans="1:4" ht="28.5">
       <c r="A3" s="2">
         <v>2</v>
       </c>
@@ -1800,7 +1255,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="4" spans="1:4">
+    <row r="4" spans="1:4" ht="28.5">
       <c r="A4" s="2">
         <v>3</v>
       </c>
@@ -1816,12 +1271,71 @@
     </row>
   </sheetData>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D2:D1048576">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D2:D1048576" xr:uid="{00000000-0002-0000-0200-000000000000}">
       <formula1>"Benar, Salah"</formula1>
     </dataValidation>
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D1"/>
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D1" xr:uid="{00000000-0002-0000-0200-000001000000}"/>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B5A0505E-DECB-47D3-8520-D506FAB11766}">
+  <dimension ref="A1:C4"/>
+  <sheetFormatPr defaultColWidth="9.125" defaultRowHeight="14.25"/>
+  <cols>
+    <col min="1" max="2" width="6.375" style="1" customWidth="1"/>
+    <col min="3" max="3" width="57.75" style="1" customWidth="1"/>
+    <col min="4" max="16384" width="9.125" style="3"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" ht="15">
+      <c r="A1" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="19" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2" s="13">
+        <v>1</v>
+      </c>
+      <c r="B2" s="21">
+        <v>1</v>
+      </c>
+      <c r="C2" s="23" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" s="13">
+        <v>2</v>
+      </c>
+      <c r="B3" s="13">
+        <v>1</v>
+      </c>
+      <c r="C3" s="22" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4" s="13">
+        <v>3</v>
+      </c>
+      <c r="B4" s="13">
+        <v>1</v>
+      </c>
+      <c r="C4" s="20" t="s">
+        <v>45</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>